--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\michi\anaconda_projects\Golf-Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29785F5-B9D6-4B5E-8DA4-815AB5FAB7F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815B33F3-6631-4FBF-9101-070DEFB6E4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="341">
   <si>
     <t>Smash Factor</t>
   </si>
@@ -1058,12 +1058,18 @@
   </si>
   <si>
     <t>04/22/26 21:15:59 pm</t>
+  </si>
+  <si>
+    <t>Swing Tempo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1107,7 +1113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1136,6 +1142,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -27865,13 +27882,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79846508-2374-4F08-916E-833A45152450}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="8.7265625" style="11"/>
+    <col min="10" max="10" width="8.7265625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -27891,7 +27909,7 @@
         <v>23</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>29</v>
@@ -27899,8 +27917,35 @@
       <c r="I1" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J1" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -27928,12 +27973,35 @@
       <c r="I2" s="6">
         <v>251</v>
       </c>
-      <c r="K2">
-        <f>D2/B2</f>
-        <v>1.4778761061946901</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J2" s="13">
+        <v>3</v>
+      </c>
+      <c r="K2" s="6">
+        <v>0</v>
+      </c>
+      <c r="L2" s="6">
+        <v>0</v>
+      </c>
+      <c r="M2" s="6">
+        <v>0</v>
+      </c>
+      <c r="N2" s="6">
+        <v>0</v>
+      </c>
+      <c r="O2" s="6">
+        <v>0</v>
+      </c>
+      <c r="P2" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="6">
+        <v>0</v>
+      </c>
+      <c r="R2" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -27961,8 +28029,35 @@
       <c r="I3" s="6">
         <v>222</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J3" s="13">
+        <v>3</v>
+      </c>
+      <c r="K3" s="6">
+        <v>0</v>
+      </c>
+      <c r="L3" s="6">
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <v>0</v>
+      </c>
+      <c r="N3" s="6">
+        <v>0</v>
+      </c>
+      <c r="O3" s="6">
+        <v>0</v>
+      </c>
+      <c r="P3" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>0</v>
+      </c>
+      <c r="R3" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -27990,8 +28085,35 @@
       <c r="I4" s="6">
         <v>210</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="J4" s="13">
+        <v>3</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0</v>
+      </c>
+      <c r="L4" s="6">
+        <v>0</v>
+      </c>
+      <c r="M4" s="6">
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <v>0</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>0</v>
+      </c>
+      <c r="R4" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
@@ -28019,8 +28141,35 @@
       <c r="I5" s="6">
         <v>206</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J5" s="13">
+        <v>2.5</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0</v>
+      </c>
+      <c r="L5" s="6">
+        <v>0</v>
+      </c>
+      <c r="M5" s="6">
+        <v>0</v>
+      </c>
+      <c r="N5" s="6">
+        <v>0</v>
+      </c>
+      <c r="O5" s="6">
+        <v>0</v>
+      </c>
+      <c r="P5" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>0</v>
+      </c>
+      <c r="R5" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
@@ -28048,8 +28197,35 @@
       <c r="I6" s="6">
         <v>194</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J6" s="13">
+        <v>2.5</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0</v>
+      </c>
+      <c r="L6" s="6">
+        <v>0</v>
+      </c>
+      <c r="M6" s="6">
+        <v>0</v>
+      </c>
+      <c r="N6" s="6">
+        <v>0</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0</v>
+      </c>
+      <c r="P6" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0</v>
+      </c>
+      <c r="R6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -28077,8 +28253,35 @@
       <c r="I7" s="6">
         <v>186</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J7" s="13">
+        <v>2.5</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0</v>
+      </c>
+      <c r="L7" s="6">
+        <v>0</v>
+      </c>
+      <c r="M7" s="6">
+        <v>0</v>
+      </c>
+      <c r="N7" s="6">
+        <v>0</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0</v>
+      </c>
+      <c r="P7" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>0</v>
+      </c>
+      <c r="R7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
@@ -28106,8 +28309,35 @@
       <c r="I8" s="6">
         <v>177</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J8" s="13">
+        <v>2.5</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+      <c r="L8" s="6">
+        <v>0</v>
+      </c>
+      <c r="M8" s="6">
+        <v>0</v>
+      </c>
+      <c r="N8" s="6">
+        <v>0</v>
+      </c>
+      <c r="O8" s="6">
+        <v>0</v>
+      </c>
+      <c r="P8" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>0</v>
+      </c>
+      <c r="R8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
@@ -28135,8 +28365,35 @@
       <c r="I9" s="6">
         <v>167</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J9" s="13">
+        <v>2.5</v>
+      </c>
+      <c r="K9" s="6">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6">
+        <v>0</v>
+      </c>
+      <c r="M9" s="6">
+        <v>0</v>
+      </c>
+      <c r="N9" s="6">
+        <v>0</v>
+      </c>
+      <c r="O9" s="6">
+        <v>0</v>
+      </c>
+      <c r="P9" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>0</v>
+      </c>
+      <c r="R9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="16" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>9</v>
       </c>
@@ -28164,8 +28421,35 @@
       <c r="I10" s="3">
         <v>157</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J10" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
@@ -28193,8 +28477,35 @@
       <c r="I11" s="6">
         <v>146</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J11" s="13">
+        <v>2.5</v>
+      </c>
+      <c r="K11" s="6">
+        <v>0</v>
+      </c>
+      <c r="L11" s="6">
+        <v>0</v>
+      </c>
+      <c r="M11" s="6">
+        <v>0</v>
+      </c>
+      <c r="N11" s="6">
+        <v>0</v>
+      </c>
+      <c r="O11" s="6">
+        <v>0</v>
+      </c>
+      <c r="P11" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>0</v>
+      </c>
+      <c r="R11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
@@ -28222,8 +28533,35 @@
       <c r="I12" s="6">
         <v>135</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="J12" s="13">
+        <v>2.5</v>
+      </c>
+      <c r="K12" s="6">
+        <v>0</v>
+      </c>
+      <c r="L12" s="6">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6">
+        <v>0</v>
+      </c>
+      <c r="N12" s="6">
+        <v>0</v>
+      </c>
+      <c r="O12" s="6">
+        <v>0</v>
+      </c>
+      <c r="P12" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>0</v>
+      </c>
+      <c r="R12" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>207</v>
       </c>
@@ -28250,6 +28588,33 @@
       </c>
       <c r="I13" s="6">
         <v>124</v>
+      </c>
+      <c r="J13" s="14">
+        <v>2</v>
+      </c>
+      <c r="K13" s="6">
+        <v>0</v>
+      </c>
+      <c r="L13" s="6">
+        <v>0</v>
+      </c>
+      <c r="M13" s="6">
+        <v>0</v>
+      </c>
+      <c r="N13" s="6">
+        <v>0</v>
+      </c>
+      <c r="O13" s="6">
+        <v>0</v>
+      </c>
+      <c r="P13" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>0</v>
+      </c>
+      <c r="R13" s="6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
